--- a/data/trans_dic/P34B04_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P34B04_R-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, 3 veces por semana o más</t>
+          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,11; 26,05</t>
+          <t>18,48; 26,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,44; 24,32</t>
+          <t>16,44; 23,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,33; 34,3</t>
+          <t>19,62; 34,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,23</t>
+          <t>1,81; 5,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,43</t>
+          <t>2,59; 6,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,58</t>
+          <t>2,05; 8,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,63; 15,15</t>
+          <t>10,61; 15,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 14,81</t>
+          <t>10,32; 14,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,34; 22,08</t>
+          <t>12,4; 21,74</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,57; 15,76</t>
+          <t>10,45; 15,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,63; 13,86</t>
+          <t>8,63; 13,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,83; 19,22</t>
+          <t>10,22; 19,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,6</t>
+          <t>0,46; 2,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,15</t>
+          <t>1,0; 3,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,96</t>
+          <t>1,35; 5,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 9,15</t>
+          <t>5,94; 8,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,17; 8,09</t>
+          <t>5,19; 8,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,84</t>
+          <t>5,62; 10,85</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,09</t>
+          <t>3,71; 7,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 7,34</t>
+          <t>3,79; 7,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,29; 13,77</t>
+          <t>8,11; 13,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,78</t>
+          <t>0,14; 1,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,94</t>
+          <t>1,01; 3,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,39</t>
+          <t>1,25; 3,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,8</t>
+          <t>2,04; 3,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,68</t>
+          <t>2,64; 4,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 8,07</t>
+          <t>5,1; 7,95</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,17</t>
+          <t>2,46; 5,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,56</t>
+          <t>1,73; 4,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,76</t>
+          <t>2,18; 7,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,9</t>
+          <t>0,33; 1,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,62</t>
+          <t>1,01; 2,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,06</t>
+          <t>1,32; 3,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,8</t>
+          <t>1,19; 2,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,69</t>
+          <t>2,23; 4,76</t>
         </is>
       </c>
     </row>
@@ -1118,32 +1118,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,26</t>
+          <t>1,09; 4,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,29</t>
+          <t>1,73; 4,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,78</t>
+          <t>0,41; 1,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,35</t>
+          <t>0,56; 2,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,71</t>
+          <t>1,31; 2,71</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,94</t>
+          <t>0,66; 4,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,44</t>
+          <t>0,49; 2,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,94</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,98</t>
+          <t>0,31; 1,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,26</t>
+          <t>0,27; 1,22</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,54</t>
+          <t>0,02; 0,57</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,56; 8,35</t>
+          <t>6,55; 8,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,22</t>
+          <t>5,51; 7,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,49; 9,71</t>
+          <t>6,44; 9,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,14</t>
+          <t>0,51; 1,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,67</t>
+          <t>0,95; 1,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,13</t>
+          <t>1,22; 2,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,56</t>
+          <t>3,52; 4,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,33; 4,22</t>
+          <t>3,3; 4,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,06; 5,6</t>
+          <t>4,11; 5,64</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, 3 veces por semana o más</t>
+          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>82014; 117990</t>
+          <t>83715; 120572</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>68951; 102012</t>
+          <t>68956; 100644</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77331; 137204</t>
+          <t>78486; 136563</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7754; 22494</t>
+          <t>7798; 22476</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10561; 25459</t>
+          <t>10238; 25646</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6978; 26731</t>
+          <t>6377; 25348</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93916; 133828</t>
+          <t>93713; 134911</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>83896; 120742</t>
+          <t>84122; 121591</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>87781; 157105</t>
+          <t>88200; 154661</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72538; 108151</t>
+          <t>71714; 107979</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50935; 81864</t>
+          <t>50973; 81087</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41639; 81400</t>
+          <t>43284; 80603</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3067; 15885</t>
+          <t>2836; 16799</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5740; 17773</t>
+          <t>5645; 18244</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7212; 25297</t>
+          <t>6901; 25632</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77886; 118641</t>
+          <t>76981; 115875</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59660; 93394</t>
+          <t>59927; 94509</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53062; 101189</t>
+          <t>52442; 101328</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24878; 48352</t>
+          <t>25270; 48952</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25812; 49111</t>
+          <t>25387; 49546</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44435; 73812</t>
+          <t>43482; 72952</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>965; 12636</t>
+          <t>970; 12562</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6608; 19415</t>
+          <t>6708; 20268</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6975; 18364</t>
+          <t>6778; 18009</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28235; 52818</t>
+          <t>28304; 54173</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34688; 62258</t>
+          <t>35172; 61848</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>53963; 86942</t>
+          <t>55000; 85702</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15091; 37908</t>
+          <t>15132; 36340</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12308; 29436</t>
+          <t>11156; 28410</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20711; 68848</t>
+          <t>19319; 68320</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4790</t>
+          <t>0; 5001</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2063; 12322</t>
+          <t>2110; 11851</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7384; 18650</t>
+          <t>7170; 18507</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15148; 37619</t>
+          <t>16257; 38375</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15861; 36244</t>
+          <t>15441; 35474</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33805; 75036</t>
+          <t>35671; 76222</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5428</t>
+          <t>0; 5613</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4729; 20368</t>
+          <t>5222; 20619</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9508; 24039</t>
+          <t>9689; 23959</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4783</t>
+          <t>0; 4833</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2198</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2325; 9735</t>
+          <t>2242; 9474</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7270</t>
+          <t>0; 7308</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5764; 22870</t>
+          <t>5411; 21514</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14097; 30020</t>
+          <t>14483; 30008</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2051; 12209</t>
+          <t>2059; 12421</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1918; 8977</t>
+          <t>1809; 8371</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2043</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>284; 5689</t>
+          <t>0; 5020</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2916; 13127</t>
+          <t>2053; 12162</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2011</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2449; 12283</t>
+          <t>2666; 11917</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2150</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4078</t>
+          <t>0; 4421</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3106</t>
+          <t>0; 3474</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 2127</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2543</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2155</t>
+          <t>0; 2678</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2141</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3652</t>
+          <t>0; 4432</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>159; 3829</t>
+          <t>158; 4065</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>224671; 286021</t>
+          <t>224157; 285987</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>188244; 245235</t>
+          <t>187002; 245684</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>224525; 335682</t>
+          <t>222724; 334839</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18256; 40677</t>
+          <t>18211; 41107</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>32736; 59222</t>
+          <t>33511; 58462</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>45189; 77880</t>
+          <t>44685; 78759</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>249277; 318599</t>
+          <t>245520; 317842</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>230891; 292819</t>
+          <t>229156; 296573</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>288626; 398663</t>
+          <t>292302; 400992</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B04_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P34B04_R-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,48; 26,62</t>
+          <t>18,28; 26,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,44; 23,99</t>
+          <t>16,09; 24,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,62; 34,14</t>
+          <t>20,57; 34,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,22</t>
+          <t>1,8; 5,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,48</t>
+          <t>2,59; 6,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,14</t>
+          <t>2,49; 9,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,61; 15,28</t>
+          <t>10,7; 15,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,32; 14,92</t>
+          <t>10,26; 14,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,4; 21,74</t>
+          <t>12,73; 21,16</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,45; 15,74</t>
+          <t>10,29; 15,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,63; 13,73</t>
+          <t>8,58; 13,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,22; 19,03</t>
+          <t>10,42; 19,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,75</t>
+          <t>0,5; 2,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,24</t>
+          <t>1,02; 3,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,02</t>
+          <t>1,92; 5,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,94; 8,94</t>
+          <t>6,09; 9,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,19</t>
+          <t>5,18; 8,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,85</t>
+          <t>6,69; 11,29</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,18</t>
+          <t>3,68; 7,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,4</t>
+          <t>3,76; 7,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,11; 13,61</t>
+          <t>7,67; 12,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,77</t>
+          <t>0,14; 1,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,06</t>
+          <t>0,9; 3,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,32</t>
+          <t>1,19; 3,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,9</t>
+          <t>2,02; 4,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,65</t>
+          <t>2,62; 4,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 7,95</t>
+          <t>4,72; 7,59</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,91</t>
+          <t>2,48; 6,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,4</t>
+          <t>1,74; 4,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,7</t>
+          <t>5,49; 9,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,83</t>
+          <t>0,32; 1,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,6</t>
+          <t>1,13; 2,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,12</t>
+          <t>1,3; 3,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,74</t>
+          <t>1,19; 2,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,76</t>
+          <t>3,47; 5,52</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -1118,22 +1118,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,31</t>
+          <t>1,16; 4,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,28</t>
+          <t>2,0; 4,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,74</t>
+          <t>0,43; 1,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,21</t>
+          <t>0,54; 2,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,71</t>
+          <t>1,33; 2,85</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,01</t>
+          <t>0,66; 4,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,27</t>
+          <t>0,48; 2,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,14; 1,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,83</t>
+          <t>0,44; 1,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,22</t>
+          <t>0,44; 1,5</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,57</t>
+          <t>0,06; 0,57</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,35</t>
+          <t>6,61; 8,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,24</t>
+          <t>5,54; 7,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,44; 9,68</t>
+          <t>7,77; 10,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,16</t>
+          <t>0,5; 1,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,65</t>
+          <t>0,94; 1,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,15</t>
+          <t>1,44; 2,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,52; 4,55</t>
+          <t>3,57; 4,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,3; 4,27</t>
+          <t>3,3; 4,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,11; 5,64</t>
+          <t>4,66; 5,99</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104465</t>
+          <t>108889</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>17462</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>118857</t>
+          <t>126351</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>83715; 120572</t>
+          <t>82792; 118799</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>68956; 100644</t>
+          <t>67483; 102287</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78486; 136563</t>
+          <t>83875; 142188</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7798; 22476</t>
+          <t>7757; 21569</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10238; 25646</t>
+          <t>10262; 25841</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6377; 25348</t>
+          <t>8985; 32630</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93713; 134911</t>
+          <t>94495; 134388</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84122; 121591</t>
+          <t>83642; 120282</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>88200; 154661</t>
+          <t>97836; 162562</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60300</t>
+          <t>67977</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14955</t>
+          <t>16188</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>75254</t>
+          <t>84165</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71714; 107979</t>
+          <t>70641; 106898</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50973; 81087</t>
+          <t>50667; 81630</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43284; 80603</t>
+          <t>49707; 91944</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2836; 16799</t>
+          <t>3054; 17799</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5645; 18244</t>
+          <t>5773; 18338</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6901; 25632</t>
+          <t>9601; 27985</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76981; 115875</t>
+          <t>78941; 119739</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59927; 94509</t>
+          <t>59723; 93962</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52442; 101328</t>
+          <t>65328; 110256</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57132</t>
+          <t>63198</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68703</t>
+          <t>75694</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25270; 48952</t>
+          <t>25075; 47989</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25387; 49546</t>
+          <t>25143; 48279</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43482; 72952</t>
+          <t>47540; 79668</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>970; 12562</t>
+          <t>976; 12111</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6708; 20268</t>
+          <t>5960; 19834</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6778; 18009</t>
+          <t>7410; 20052</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28304; 54173</t>
+          <t>28092; 56048</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35172; 61848</t>
+          <t>34798; 61668</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55000; 85702</t>
+          <t>58549; 94143</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44700</t>
+          <t>50445</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11608</t>
+          <t>12988</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>56308</t>
+          <t>63432</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15132; 36340</t>
+          <t>15221; 36906</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11156; 28410</t>
+          <t>11253; 28990</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19319; 68320</t>
+          <t>38454; 67438</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5001</t>
+          <t>0; 3877</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2110; 11851</t>
+          <t>2107; 12320</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7170; 18507</t>
+          <t>8314; 19495</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16257; 38375</t>
+          <t>16006; 38109</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15441; 35474</t>
+          <t>15476; 34735</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35671; 76222</t>
+          <t>49861; 79285</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20843</t>
+          <t>24837</t>
         </is>
       </c>
     </row>
@@ -2402,22 +2402,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5613</t>
+          <t>0; 5725</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5222; 20619</t>
+          <t>5544; 22278</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9689; 23959</t>
+          <t>12161; 28854</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4833</t>
+          <t>0; 5542</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2427,22 +2427,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2242; 9474</t>
+          <t>2591; 10466</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7308</t>
+          <t>0; 7395</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5411; 21514</t>
+          <t>5273; 19928</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14483; 30008</t>
+          <t>16140; 34652</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>7002</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2059; 12421</t>
+          <t>2029; 13229</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1809; 8371</t>
+          <t>1972; 9538</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5020</t>
+          <t>628; 5638</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2053; 12162</t>
+          <t>2925; 13074</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2666; 11917</t>
+          <t>3756; 12675</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>663</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>928</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1591</t>
         </is>
       </c>
     </row>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4421</t>
+          <t>0; 4738</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3474</t>
+          <t>0; 3657</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2678</t>
+          <t>0; 3102</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 4432</t>
+          <t>0; 4100</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>158; 4065</t>
+          <t>427; 4416</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>287401</t>
+          <t>315145</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60263</t>
+          <t>67927</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>347664</t>
+          <t>383072</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>224157; 285987</t>
+          <t>226287; 287613</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>187002; 245684</t>
+          <t>187975; 243386</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>222724; 334839</t>
+          <t>274244; 360886</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18211; 41107</t>
+          <t>17891; 41586</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>33511; 58462</t>
+          <t>33294; 58771</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>44685; 78759</t>
+          <t>53587; 86655</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>245520; 317842</t>
+          <t>248887; 315449</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>229156; 296573</t>
+          <t>229198; 293767</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>292302; 400992</t>
+          <t>338497; 435086</t>
         </is>
       </c>
     </row>
